--- a/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/In/cfg_att_info.xlsx
+++ b/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/In/cfg_att_info.xlsx
@@ -3,8 +3,13 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\天使之战\tszz_GMTest\engine_package\Res\MuDataEditor\天使之战_v1.0.0.0\In\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="11175"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="cfg_att_info" sheetId="1" r:id="rId1"/>
@@ -7492,9 +7497,6 @@
       <c r="N40" s="6">
         <v>200011</v>
       </c>
-      <c r="T40" s="6">
-        <v>3</v>
-      </c>
     </row>
     <row r="41" s="6" customFormat="1" spans="1:21">
       <c r="A41" s="6">
@@ -7601,9 +7603,6 @@
       <c r="N42" s="6">
         <v>200021</v>
       </c>
-      <c r="T42" s="6">
-        <v>5</v>
-      </c>
     </row>
     <row r="43" s="6" customFormat="1" spans="1:21">
       <c r="A43" s="6">
@@ -11211,7 +11210,7 @@
         <v>10</v>
       </c>
       <c r="P102" s="24">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q102" s="24">
         <v>6</v>
@@ -11223,7 +11222,7 @@
         <v>17</v>
       </c>
       <c r="T102" s="24">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="U102" s="24">
         <v>8</v>
